--- a/entrepreneur_forms/004_vendor_satisfaction_survey_form--entrepreneur_forms.xlsx
+++ b/entrepreneur_forms/004_vendor_satisfaction_survey_form--entrepreneur_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -757,8 +757,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -786,12 +786,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'vendor_1'}</t>
+          <t>vendor_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Vendor 1'}</t>
+          <t>Vendor 1</t>
         </is>
       </c>
     </row>
@@ -803,12 +803,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'vendor_2'}</t>
+          <t>vendor_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Vendor 2'}</t>
+          <t>Vendor 2</t>
         </is>
       </c>
     </row>
@@ -820,12 +820,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'vendor_3'}</t>
+          <t>vendor_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Vendor 3'}</t>
+          <t>Vendor 3</t>
         </is>
       </c>
     </row>
@@ -837,12 +837,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'very_good'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Very Good'}</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'not_good'}</t>
+          <t>not_good</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Not Good'}</t>
+          <t>Not Good</t>
         </is>
       </c>
     </row>
@@ -905,12 +905,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'very_likely'}</t>
+          <t>very_likely</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Very Likely'}</t>
+          <t>Very Likely</t>
         </is>
       </c>
     </row>
@@ -922,12 +922,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'not_likely'}</t>
+          <t>not_likely</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Not Likely'}</t>
+          <t>Not Likely</t>
         </is>
       </c>
     </row>
@@ -939,12 +939,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'not_likely_at_all'}</t>
+          <t>not_likely_at_all</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Not Likely at All'}</t>
+          <t>Not Likely at All</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'undecided'}</t>
+          <t>undecided</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Undecided'}</t>
+          <t>Undecided</t>
         </is>
       </c>
     </row>
@@ -973,12 +973,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'price'}</t>
+          <t>price</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Price'}</t>
+          <t>Price</t>
         </is>
       </c>
     </row>
@@ -990,12 +990,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'quality'}</t>
+          <t>quality</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Quality'}</t>
+          <t>Quality</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'service'}</t>
+          <t>service</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Service'}</t>
+          <t>Service</t>
         </is>
       </c>
     </row>
@@ -1024,12 +1024,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1041,12 +1041,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
